--- a/pdn_project_allocation/testdata/test7_eligibility.xlsx
+++ b/pdn_project_allocation/testdata/test7_eligibility.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Supervisors" sheetId="1" state="visible" r:id="rId2"/>
@@ -173,9 +173,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -193,11 +193,17 @@
       <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -211,7 +217,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.21"/>
@@ -286,7 +292,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -300,7 +306,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
@@ -433,7 +439,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -447,7 +453,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
@@ -494,7 +500,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -508,7 +514,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
@@ -641,7 +647,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
